--- a/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T10:05:30+00:00</t>
+    <t>2026-03-13T14:11:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T14:11:35+00:00</t>
+    <t>2026-03-13T17:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:00:40+00:00</t>
+    <t>2026-03-13T17:26:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:39+00:00</t>
+    <t>2026-03-13T17:26:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:16+00:00</t>
+    <t>2026-03-13T22:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.0-snapsnot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T22:26:12+00:00</t>
+    <t>2026-03-20T08:18:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T08:18:16+00:00</t>
+    <t>2026-03-23T13:14:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T13:14:10+00:00</t>
+    <t>2026-03-27T09:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T07:16:03+00:00</t>
+    <t>2026-04-01T07:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:43:12+00:00</t>
+    <t>2026-04-02T07:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:21:27+00:00</t>
+    <t>2026-04-02T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:41:19+00:00</t>
+    <t>2026-04-07T08:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T08:23:13+00:00</t>
+    <t>2026-04-15T13:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T15:41:19+00:00</t>
+    <t>2026-04-20T15:11:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$70</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2586" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2550" uniqueCount="445">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -498,13 +498,6 @@
 &lt;/valueIdentifier&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:system}
-</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>Event.identifier</t>
   </si>
   <si>
@@ -512,15 +505,6 @@
   </si>
   <si>
     <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>Consent.identifier:mainIdentifier</t>
-  </si>
-  <si>
-    <t>mainIdentifier</t>
-  </si>
-  <si>
-    <t>Identifiant de la directive anticipée</t>
   </si>
   <si>
     <t>Consent.status</t>
@@ -807,6 +791,9 @@
   </si>
   <si>
     <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -1739,7 +1726,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN71"/>
+  <dimension ref="A1:AN70"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.65625" customWidth="true" bestFit="true"/>
@@ -2944,13 +2931,13 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>79</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>77</v>
@@ -3006,14 +2993,16 @@
         <v>77</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="AC11" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AD11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>153</v>
+        <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
         <v>146</v>
@@ -3031,28 +3020,26 @@
         <v>101</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM11" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AN11" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AL11" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM11" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="AN11" t="s" s="2">
-        <v>156</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
         <v>77</v>
       </c>
@@ -3067,24 +3054,26 @@
         <v>90</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>147</v>
+        <v>109</v>
       </c>
       <c r="L12" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="O12" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="M12" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>77</v>
       </c>
@@ -3096,7 +3085,7 @@
         <v>77</v>
       </c>
       <c r="T12" t="s" s="2">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="U12" t="s" s="2">
         <v>77</v>
@@ -3108,13 +3097,13 @@
         <v>77</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>77</v>
+        <v>160</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>77</v>
+        <v>161</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>77</v>
+        <v>162</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>77</v>
@@ -3132,13 +3121,13 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>77</v>
@@ -3147,24 +3136,24 @@
         <v>101</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>156</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3187,20 +3176,16 @@
         <v>90</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>109</v>
+        <v>168</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>164</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>77</v>
       </c>
@@ -3209,7 +3194,7 @@
         <v>77</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>77</v>
+        <v>171</v>
       </c>
       <c r="T13" t="s" s="2">
         <v>77</v>
@@ -3224,31 +3209,31 @@
         <v>77</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="Z13" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>89</v>
@@ -3263,24 +3248,24 @@
         <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>168</v>
+        <v>77</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>169</v>
+        <v>77</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>170</v>
+        <v>77</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>171</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3291,25 +3276,25 @@
         <v>89</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="J14" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3321,7 +3306,7 @@
         <v>77</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="T14" t="s" s="2">
         <v>77</v>
@@ -3336,7 +3321,7 @@
         <v>77</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="Y14" t="s" s="2">
         <v>178</v>
@@ -3360,13 +3345,13 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>77</v>
@@ -3375,24 +3360,24 @@
         <v>101</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>77</v>
+        <v>181</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>77</v>
+        <v>182</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>77</v>
+        <v>183</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3400,10 +3385,10 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G15" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="G15" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>77</v>
@@ -3415,15 +3400,17 @@
         <v>90</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>187</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>77</v>
@@ -3448,37 +3435,37 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>177</v>
+        <v>77</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>183</v>
+        <v>77</v>
       </c>
       <c r="Z15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="AA15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>180</v>
-      </c>
       <c r="AG15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH15" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="AH15" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>77</v>
@@ -3487,24 +3474,24 @@
         <v>101</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>186</v>
+        <v>77</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3518,7 +3505,7 @@
         <v>89</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>77</v>
@@ -3527,16 +3514,16 @@
         <v>90</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3586,7 +3573,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3601,38 +3588,38 @@
         <v>101</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>77</v>
+        <v>198</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>77</v>
@@ -3641,16 +3628,16 @@
         <v>90</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3700,13 +3687,13 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>77</v>
@@ -3715,28 +3702,28 @@
         <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>204</v>
+        <v>77</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3755,17 +3742,15 @@
         <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>211</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -3814,7 +3799,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3829,35 +3814,35 @@
         <v>101</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>213</v>
+        <v>77</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>216</v>
+        <v>77</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>77</v>
@@ -3877,7 +3862,9 @@
       <c r="M19" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="N19" s="2"/>
+      <c r="N19" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -3914,25 +3901,23 @@
         <v>77</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="AC19" s="2"/>
       <c r="AD19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>77</v>
+        <v>222</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>77</v>
@@ -3941,26 +3926,28 @@
         <v>101</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>212</v>
+        <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>77</v>
+        <v>223</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>220</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>216</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="D20" t="s" s="2">
         <v>77</v>
       </c>
@@ -3972,7 +3959,7 @@
         <v>89</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>77</v>
@@ -3981,16 +3968,16 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4028,17 +4015,19 @@
         <v>77</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="AC20" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AD20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>227</v>
+        <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4056,7 +4045,7 @@
         <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
@@ -4067,13 +4056,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="C21" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="C21" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>77</v>
@@ -4095,16 +4084,16 @@
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="L21" t="s" s="2">
-        <v>232</v>
-      </c>
       <c r="M21" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4154,7 +4143,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4172,7 +4161,7 @@
         <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>77</v>
@@ -4181,16 +4170,14 @@
         <v>77</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="B22" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="B22" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>234</v>
-      </c>
+      <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>77</v>
       </c>
@@ -4202,26 +4189,24 @@
         <v>89</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="M22" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>225</v>
-      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -4270,7 +4255,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4282,16 +4267,16 @@
         <v>77</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>228</v>
+        <v>77</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>77</v>
+        <v>238</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>77</v>
@@ -4299,21 +4284,21 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>77</v>
@@ -4325,15 +4310,17 @@
         <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>239</v>
+        <v>135</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>240</v>
+        <v>136</v>
       </c>
       <c r="M23" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="N23" s="2"/>
+      <c r="N23" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -4370,31 +4357,31 @@
         <v>77</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>77</v>
+        <v>242</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>77</v>
+        <v>243</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>77</v>
+        <v>244</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>77</v>
@@ -4403,7 +4390,7 @@
         <v>77</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>77</v>
@@ -4411,21 +4398,21 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>77</v>
@@ -4434,21 +4421,21 @@
         <v>77</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>136</v>
+        <v>248</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
       </c>
@@ -4460,7 +4447,7 @@
         <v>77</v>
       </c>
       <c r="T24" t="s" s="2">
-        <v>77</v>
+        <v>251</v>
       </c>
       <c r="U24" t="s" s="2">
         <v>77</v>
@@ -4472,52 +4459,52 @@
         <v>77</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>77</v>
+        <v>160</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>77</v>
+        <v>252</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>77</v>
+        <v>253</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>247</v>
+        <v>77</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>248</v>
+        <v>77</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>153</v>
+        <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>77</v>
+        <v>255</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>77</v>
@@ -4525,10 +4512,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4554,14 +4541,14 @@
         <v>109</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4574,7 +4561,7 @@
         <v>77</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="U25" t="s" s="2">
         <v>77</v>
@@ -4586,13 +4573,13 @@
         <v>77</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>165</v>
+        <v>113</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>256</v>
+        <v>114</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>257</v>
+        <v>115</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>77</v>
@@ -4610,7 +4597,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4628,10 +4615,10 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>259</v>
+        <v>77</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>77</v>
@@ -4639,10 +4626,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4662,20 +4649,22 @@
         <v>77</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>109</v>
+        <v>267</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="O26" t="s" s="2">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4688,7 +4677,7 @@
         <v>77</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>266</v>
+        <v>77</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>77</v>
@@ -4700,13 +4689,13 @@
         <v>77</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>77</v>
@@ -4724,7 +4713,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4742,10 +4731,10 @@
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>77</v>
+        <v>273</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>77</v>
@@ -4753,10 +4742,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4776,22 +4765,22 @@
         <v>77</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4804,7 +4793,7 @@
         <v>77</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>77</v>
+        <v>282</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>77</v>
@@ -4840,7 +4829,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4858,10 +4847,10 @@
         <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>77</v>
@@ -4869,10 +4858,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4895,19 +4884,19 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -4920,7 +4909,7 @@
         <v>77</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>286</v>
+        <v>77</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>77</v>
@@ -4956,7 +4945,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4974,10 +4963,10 @@
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>288</v>
+        <v>77</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>77</v>
@@ -4985,10 +4974,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5011,19 +5000,19 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>292</v>
+        <v>267</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -5072,7 +5061,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5093,7 +5082,7 @@
         <v>77</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>77</v>
@@ -5101,10 +5090,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5127,19 +5116,17 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>271</v>
+        <v>234</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>303</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -5152,7 +5139,7 @@
         <v>77</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>77</v>
+        <v>308</v>
       </c>
       <c r="U30" t="s" s="2">
         <v>77</v>
@@ -5188,7 +5175,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5209,7 +5196,7 @@
         <v>77</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>
@@ -5217,10 +5204,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5243,17 +5230,17 @@
         <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>239</v>
+        <v>193</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -5266,7 +5253,7 @@
         <v>77</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>312</v>
+        <v>77</v>
       </c>
       <c r="U31" t="s" s="2">
         <v>77</v>
@@ -5302,7 +5289,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5323,7 +5310,7 @@
         <v>77</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>314</v>
+        <v>294</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -5331,10 +5318,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5345,7 +5332,7 @@
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>77</v>
@@ -5354,21 +5341,19 @@
         <v>77</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>198</v>
+        <v>318</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="N32" s="2"/>
-      <c r="O32" t="s" s="2">
-        <v>319</v>
-      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>77</v>
       </c>
@@ -5416,13 +5401,13 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>77</v>
@@ -5437,7 +5422,7 @@
         <v>77</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>298</v>
+        <v>77</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>77</v>
@@ -5459,7 +5444,7 @@
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>77</v>
@@ -5471,13 +5456,13 @@
         <v>77</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>322</v>
+        <v>234</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>323</v>
+        <v>235</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>324</v>
+        <v>236</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5528,19 +5513,19 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>321</v>
+        <v>237</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>77</v>
@@ -5549,7 +5534,7 @@
         <v>77</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>77</v>
+        <v>238</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>77</v>
@@ -5557,21 +5542,21 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>77</v>
@@ -5583,15 +5568,17 @@
         <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>239</v>
+        <v>135</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>240</v>
+        <v>136</v>
       </c>
       <c r="M34" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="N34" s="2"/>
+      <c r="N34" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5640,19 +5627,19 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>77</v>
@@ -5661,7 +5648,7 @@
         <v>77</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>77</v>
@@ -5669,14 +5656,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>134</v>
+        <v>324</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5689,24 +5676,26 @@
         <v>77</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>136</v>
+        <v>325</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>246</v>
+        <v>326</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="O35" s="2"/>
+      <c r="O35" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
       </c>
@@ -5754,7 +5743,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>249</v>
+        <v>327</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5775,7 +5764,7 @@
         <v>77</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>243</v>
+        <v>132</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>77</v>
@@ -5783,33 +5772,33 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>328</v>
+        <v>77</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>135</v>
+        <v>103</v>
       </c>
       <c r="L36" t="s" s="2">
         <v>329</v>
@@ -5817,12 +5806,8 @@
       <c r="M36" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="N36" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>144</v>
-      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>77</v>
       </c>
@@ -5870,19 +5855,19 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI36" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="AG36" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI36" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="AJ36" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>77</v>
@@ -5891,7 +5876,7 @@
         <v>77</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>77</v>
@@ -5931,9 +5916,11 @@
         <v>333</v>
       </c>
       <c r="M37" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="N37" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -5991,7 +5978,7 @@
         <v>89</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>101</v>
@@ -6011,10 +5998,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6034,21 +6021,23 @@
         <v>77</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>103</v>
+        <v>168</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="N38" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="O38" s="2"/>
+      <c r="O38" t="s" s="2">
+        <v>339</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>77</v>
       </c>
@@ -6072,13 +6061,13 @@
         <v>77</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>77</v>
+        <v>172</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>77</v>
+        <v>340</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>77</v>
+        <v>341</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>77</v>
@@ -6096,7 +6085,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6105,7 +6094,7 @@
         <v>89</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>101</v>
@@ -6125,10 +6114,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6139,7 +6128,7 @@
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>77</v>
@@ -6151,20 +6140,16 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>173</v>
+        <v>318</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>343</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>77</v>
       </c>
@@ -6188,13 +6173,13 @@
         <v>77</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>177</v>
+        <v>77</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>344</v>
+        <v>77</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>345</v>
+        <v>77</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>77</v>
@@ -6212,16 +6197,16 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>335</v>
+        <v>77</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>101</v>
@@ -6241,10 +6226,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6255,7 +6240,7 @@
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>77</v>
@@ -6264,16 +6249,16 @@
         <v>77</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>322</v>
+        <v>234</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>347</v>
+        <v>235</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>348</v>
+        <v>236</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6324,19 +6309,19 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>346</v>
+        <v>237</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>77</v>
@@ -6345,7 +6330,7 @@
         <v>77</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>77</v>
+        <v>238</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>77</v>
@@ -6353,21 +6338,21 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>77</v>
@@ -6379,15 +6364,17 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>239</v>
+        <v>135</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>240</v>
+        <v>136</v>
       </c>
       <c r="M41" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="N41" s="2"/>
+      <c r="N41" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>77</v>
@@ -6436,19 +6423,19 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>77</v>
@@ -6457,7 +6444,7 @@
         <v>77</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>77</v>
@@ -6465,14 +6452,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>134</v>
+        <v>324</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6485,24 +6472,26 @@
         <v>77</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>136</v>
+        <v>325</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>246</v>
+        <v>326</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="O42" s="2"/>
+      <c r="O42" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>77</v>
       </c>
@@ -6550,7 +6539,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>249</v>
+        <v>327</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6571,7 +6560,7 @@
         <v>77</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>243</v>
+        <v>132</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>77</v>
@@ -6579,46 +6568,42 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>328</v>
+        <v>77</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="J43" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>135</v>
+        <v>349</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>329</v>
+        <v>350</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>77</v>
       </c>
@@ -6666,19 +6651,19 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>331</v>
+        <v>348</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>77</v>
@@ -6687,7 +6672,7 @@
         <v>77</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>77</v>
@@ -6706,7 +6691,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>89</v>
@@ -6718,7 +6703,7 @@
         <v>77</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
         <v>353</v>
@@ -6781,7 +6766,7 @@
         <v>352</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>89</v>
@@ -6833,13 +6818,13 @@
         <v>77</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6917,12 +6902,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6936,22 +6921,22 @@
         <v>89</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>198</v>
+        <v>318</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7002,7 +6987,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7029,12 +7014,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7048,22 +7033,22 @@
         <v>89</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>322</v>
+        <v>234</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>364</v>
+        <v>235</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>365</v>
+        <v>236</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7114,7 +7099,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>363</v>
+        <v>237</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7126,7 +7111,7 @@
         <v>77</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>77</v>
@@ -7135,7 +7120,7 @@
         <v>77</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>77</v>
+        <v>238</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>77</v>
@@ -7143,21 +7128,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>77</v>
@@ -7169,15 +7154,17 @@
         <v>77</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>239</v>
+        <v>135</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>240</v>
+        <v>136</v>
       </c>
       <c r="M48" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="N48" s="2"/>
+      <c r="N48" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -7226,19 +7213,19 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>77</v>
@@ -7247,7 +7234,7 @@
         <v>77</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>77</v>
@@ -7255,14 +7242,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>134</v>
+        <v>324</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7275,24 +7262,26 @@
         <v>77</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>136</v>
+        <v>325</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>246</v>
+        <v>326</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="O49" s="2"/>
+      <c r="O49" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>77</v>
       </c>
@@ -7340,7 +7329,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>249</v>
+        <v>327</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7361,7 +7350,7 @@
         <v>77</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>243</v>
+        <v>132</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>77</v>
@@ -7369,46 +7358,42 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>328</v>
+        <v>77</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="J50" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>329</v>
+        <v>366</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>77</v>
       </c>
@@ -7432,13 +7417,13 @@
         <v>77</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>77</v>
+        <v>160</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>77</v>
+        <v>368</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>77</v>
+        <v>369</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>77</v>
@@ -7456,19 +7441,19 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>331</v>
+        <v>365</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>77</v>
@@ -7477,7 +7462,7 @@
         <v>77</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
@@ -7485,10 +7470,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7511,13 +7496,13 @@
         <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>109</v>
+        <v>371</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7544,13 +7529,13 @@
         <v>77</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>372</v>
+        <v>77</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>373</v>
+        <v>77</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>77</v>
@@ -7568,7 +7553,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7611,7 +7596,7 @@
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>77</v>
@@ -7620,23 +7605,25 @@
         <v>77</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q52" s="2"/>
+      <c r="Q52" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="R52" t="s" s="2">
         <v>77</v>
       </c>
@@ -7686,7 +7673,7 @@
         <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>77</v>
@@ -7723,7 +7710,7 @@
         <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>77</v>
@@ -7735,22 +7722,20 @@
         <v>77</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>322</v>
+        <v>234</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>379</v>
+        <v>235</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>380</v>
+        <v>236</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q53" t="s" s="2">
-        <v>381</v>
-      </c>
+      <c r="Q53" s="2"/>
       <c r="R53" t="s" s="2">
         <v>77</v>
       </c>
@@ -7794,19 +7779,19 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>378</v>
+        <v>237</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>77</v>
@@ -7815,7 +7800,7 @@
         <v>77</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>77</v>
+        <v>238</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>77</v>
@@ -7823,21 +7808,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>77</v>
@@ -7849,15 +7834,17 @@
         <v>77</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>239</v>
+        <v>135</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>240</v>
+        <v>136</v>
       </c>
       <c r="M54" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="N54" s="2"/>
+      <c r="N54" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -7906,19 +7893,19 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>77</v>
@@ -7927,7 +7914,7 @@
         <v>77</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>77</v>
@@ -7935,14 +7922,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>134</v>
+        <v>324</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7955,24 +7942,26 @@
         <v>77</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>136</v>
+        <v>325</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>246</v>
+        <v>326</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="O55" s="2"/>
+      <c r="O55" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>77</v>
       </c>
@@ -8020,7 +8009,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>249</v>
+        <v>327</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8041,7 +8030,7 @@
         <v>77</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>243</v>
+        <v>132</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>77</v>
@@ -8049,46 +8038,42 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>328</v>
+        <v>77</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>135</v>
+        <v>168</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>329</v>
+        <v>382</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>383</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>77</v>
       </c>
@@ -8112,13 +8097,13 @@
         <v>77</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>77</v>
+        <v>172</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>77</v>
+        <v>384</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>77</v>
+        <v>385</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>77</v>
@@ -8136,19 +8121,19 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>331</v>
+        <v>381</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>77</v>
@@ -8157,7 +8142,7 @@
         <v>77</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>77</v>
@@ -8165,10 +8150,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8191,13 +8176,13 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>173</v>
+        <v>387</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8224,13 +8209,13 @@
         <v>77</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>177</v>
+        <v>77</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>388</v>
+        <v>77</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>389</v>
+        <v>77</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>77</v>
@@ -8248,7 +8233,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>89</v>
@@ -8288,10 +8273,10 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>77</v>
@@ -8300,23 +8285,27 @@
         <v>77</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q58" s="2"/>
+      <c r="Q58" t="s" s="2">
+        <v>394</v>
+      </c>
       <c r="R58" t="s" s="2">
         <v>77</v>
       </c>
@@ -8336,13 +8325,13 @@
         <v>77</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>77</v>
+        <v>395</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>77</v>
+        <v>396</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>77</v>
+        <v>397</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>77</v>
@@ -8363,10 +8352,10 @@
         <v>390</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>77</v>
@@ -8389,10 +8378,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8415,68 +8404,66 @@
         <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>173</v>
+        <v>399</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q59" t="s" s="2">
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF59" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="R59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8505,10 +8492,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8531,16 +8518,16 @@
         <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8566,13 +8553,13 @@
         <v>77</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>77</v>
@@ -8590,7 +8577,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8619,10 +8606,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8645,16 +8632,16 @@
         <v>90</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8680,13 +8667,13 @@
         <v>77</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>77</v>
@@ -8704,7 +8691,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8733,10 +8720,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8759,16 +8746,16 @@
         <v>90</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>403</v>
+        <v>168</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8794,13 +8781,11 @@
         <v>77</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>419</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="Y62" s="2"/>
       <c r="Z62" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>77</v>
@@ -8818,7 +8803,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8847,10 +8832,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8861,7 +8846,7 @@
         <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>77</v>
@@ -8873,16 +8858,16 @@
         <v>90</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>173</v>
+        <v>371</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -8908,11 +8893,13 @@
         <v>77</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="Y63" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z63" t="s" s="2">
-        <v>425</v>
+        <v>77</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>77</v>
@@ -8930,13 +8917,13 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>77</v>
@@ -8973,7 +8960,7 @@
         <v>78</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>77</v>
@@ -8985,7 +8972,7 @@
         <v>90</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>375</v>
+        <v>318</v>
       </c>
       <c r="L64" t="s" s="2">
         <v>427</v>
@@ -8993,14 +8980,14 @@
       <c r="M64" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="N64" t="s" s="2">
-        <v>429</v>
-      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q64" s="2"/>
+      <c r="Q64" t="s" s="2">
+        <v>429</v>
+      </c>
       <c r="R64" t="s" s="2">
         <v>77</v>
       </c>
@@ -9050,7 +9037,7 @@
         <v>78</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>77</v>
@@ -9065,7 +9052,7 @@
         <v>77</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>77</v>
+        <v>190</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>77</v>
@@ -9087,7 +9074,7 @@
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>77</v>
@@ -9096,25 +9083,23 @@
         <v>77</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>322</v>
+        <v>234</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>431</v>
+        <v>235</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>432</v>
+        <v>236</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q65" t="s" s="2">
-        <v>433</v>
-      </c>
+      <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
         <v>77</v>
       </c>
@@ -9158,19 +9143,19 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>430</v>
+        <v>237</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>77</v>
@@ -9179,7 +9164,7 @@
         <v>77</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>195</v>
+        <v>238</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>77</v>
@@ -9187,21 +9172,21 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>77</v>
@@ -9213,15 +9198,17 @@
         <v>77</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>239</v>
+        <v>135</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>240</v>
+        <v>136</v>
       </c>
       <c r="M66" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="N66" s="2"/>
+      <c r="N66" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>77</v>
@@ -9270,19 +9257,19 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>77</v>
@@ -9291,7 +9278,7 @@
         <v>77</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>77</v>
@@ -9299,14 +9286,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>134</v>
+        <v>324</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9319,24 +9306,26 @@
         <v>77</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K67" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>136</v>
+        <v>325</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>246</v>
+        <v>326</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="O67" s="2"/>
+      <c r="O67" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>77</v>
       </c>
@@ -9384,7 +9373,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>249</v>
+        <v>327</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9405,7 +9394,7 @@
         <v>77</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>243</v>
+        <v>132</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>77</v>
@@ -9413,46 +9402,42 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>328</v>
+        <v>77</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="J68" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>329</v>
+        <v>434</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>435</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>77</v>
       </c>
@@ -9476,13 +9461,13 @@
         <v>77</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>77</v>
+        <v>160</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>77</v>
+        <v>436</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>77</v>
+        <v>437</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>77</v>
@@ -9500,19 +9485,19 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>331</v>
+        <v>433</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>77</v>
@@ -9521,7 +9506,7 @@
         <v>77</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>77</v>
@@ -9529,10 +9514,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9555,13 +9540,13 @@
         <v>90</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>109</v>
+        <v>439</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9588,13 +9573,13 @@
         <v>77</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>440</v>
+        <v>77</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>441</v>
+        <v>77</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>77</v>
@@ -9612,7 +9597,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>89</v>
@@ -9652,10 +9637,10 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>77</v>
@@ -9664,16 +9649,16 @@
         <v>77</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9727,10 +9712,10 @@
         <v>442</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>77</v>
@@ -9751,120 +9736,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="71" hidden="true">
-      <c r="A71" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="C71" s="2"/>
-      <c r="D71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E71" s="2"/>
-      <c r="F71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
-      <c r="P71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q71" s="2"/>
-      <c r="R71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="AG71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ71" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AN71">
+  <autoFilter ref="A1:AN70">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9874,7 +9747,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI70">
+  <conditionalFormatting sqref="A2:AI69">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
